--- a/data/trans_orig/IP3105-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP3105-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de tomar yogures en 2007 (tasa de respuesta: 98,79%)</t>
+          <t>Menores según la frecuencia de tomar yogures o petit suises en 2007 (tasa de respuesta: 98,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>922</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7424</t>
+          <t>7704</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5171</t>
+          <t>5346</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>1895</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9970</t>
+          <t>9701</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2149</t>
+          <t>2234</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10614</t>
+          <t>10183</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1311</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7268</t>
+          <t>7035</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4719</t>
+          <t>4810</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14457</t>
+          <t>14243</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9729</t>
+          <t>9769</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22084</t>
+          <t>21697</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12151</t>
+          <t>11944</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24532</t>
+          <t>24747</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>24008</t>
+          <t>24415</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>41780</t>
+          <t>42821</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,8%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26684</t>
+          <t>26791</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43569</t>
+          <t>43345</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30732</t>
+          <t>30939</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47900</t>
+          <t>47651</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>61611</t>
+          <t>61051</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>85863</t>
+          <t>85388</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,5%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>63096</t>
+          <t>64208</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>81683</t>
+          <t>82560</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>63,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>68812</t>
+          <t>69316</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>87275</t>
+          <t>88217</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>62,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>137496</t>
+          <t>137938</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>165547</t>
+          <t>164733</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>60,77%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>644</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5774</t>
+          <t>5312</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>6829</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2463</t>
+          <t>2370</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9516</t>
+          <t>9389</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3659</t>
+          <t>3886</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11690</t>
+          <t>12452</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2443</t>
+          <t>2514</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9488</t>
+          <t>9610</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7387</t>
+          <t>7635</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18237</t>
+          <t>18915</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13477</t>
+          <t>13775</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26339</t>
+          <t>27063</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15594</t>
+          <t>15564</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29678</t>
+          <t>29089</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>32389</t>
+          <t>32668</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>52808</t>
+          <t>51241</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26938</t>
+          <t>26349</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42984</t>
+          <t>43782</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37707</t>
+          <t>37135</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57305</t>
+          <t>57069</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>69025</t>
+          <t>69640</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>94442</t>
+          <t>95421</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,92%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>108331</t>
+          <t>107078</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>128245</t>
+          <t>127499</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>113992</t>
+          <t>114160</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>135977</t>
+          <t>136447</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>228713</t>
+          <t>228135</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>258780</t>
+          <t>259086</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>67,66%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8856</t>
+          <t>9091</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1421</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8354</t>
+          <t>7986</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4745</t>
+          <t>4787</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14277</t>
+          <t>14103</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5559</t>
+          <t>5086</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>1124</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6767</t>
+          <t>6673</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9192</t>
+          <t>8752</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7208</t>
+          <t>7248</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17475</t>
+          <t>17197</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8836</t>
+          <t>8085</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>20224</t>
+          <t>19638</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>17703</t>
+          <t>18360</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>33186</t>
+          <t>33128</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,61%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13348</t>
+          <t>12725</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25335</t>
+          <t>25160</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16742</t>
+          <t>16049</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30970</t>
+          <t>30010</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32773</t>
+          <t>32713</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>50438</t>
+          <t>50373</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,17%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>81277</t>
+          <t>81932</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>97179</t>
+          <t>98363</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>83455</t>
+          <t>84129</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>101359</t>
+          <t>101253</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>171132</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>193820</t>
+          <t>195112</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>74,25%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>791</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7604</t>
+          <t>7519</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7221</t>
+          <t>7311</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3301</t>
+          <t>3378</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12416</t>
+          <t>11615</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2848</t>
+          <t>2958</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>11531</t>
+          <t>12007</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3880</t>
+          <t>3844</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>12774</t>
+          <t>13057</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8347</t>
+          <t>8367</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>19952</t>
+          <t>20248</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10135</t>
+          <t>10890</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>23132</t>
+          <t>23585</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14811</t>
+          <t>15004</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>29698</t>
+          <t>29306</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>29025</t>
+          <t>28704</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>48042</t>
+          <t>48329</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,36%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>35372</t>
+          <t>34166</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>54744</t>
+          <t>54767</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>25231</t>
+          <t>25054</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>41154</t>
+          <t>40888</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>63657</t>
+          <t>64291</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>92089</t>
+          <t>90768</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,21%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>116675</t>
+          <t>116455</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>138793</t>
+          <t>139399</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>119550</t>
+          <t>119718</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>139636</t>
+          <t>140401</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>241814</t>
+          <t>239712</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>274105</t>
+          <t>272179</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>69,61%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7732</t>
+          <t>7641</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>19092</t>
+          <t>19385</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7905</t>
+          <t>7675</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>19265</t>
+          <t>18297</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>17860</t>
+          <t>17782</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>33237</t>
+          <t>34329</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>13793</t>
+          <t>13575</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>28424</t>
+          <t>27865</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>12567</t>
+          <t>12438</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>25577</t>
+          <t>26035</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>29672</t>
+          <t>29509</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>49553</t>
+          <t>50067</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>50256</t>
+          <t>50336</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>74477</t>
+          <t>74879</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>61339</t>
+          <t>62027</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>87737</t>
+          <t>88943</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>119197</t>
+          <t>118977</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>153924</t>
+          <t>154892</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,84%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>116234</t>
+          <t>115779</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>148886</t>
+          <t>149588</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>124782</t>
+          <t>123163</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>157527</t>
+          <t>158510</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>248956</t>
+          <t>250947</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>297311</t>
+          <t>299340</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,89%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>389610</t>
+          <t>386466</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>427272</t>
+          <t>428046</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>406411</t>
+          <t>405213</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>447524</t>
+          <t>446018</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>807311</t>
+          <t>804242</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>862470</t>
+          <t>862167</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>65,93%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de tomar yogures en 2012 (tasa de respuesta: 99,07%)</t>
+          <t>Menores según la frecuencia de tomar yogures o petit suises en 2012 (tasa de respuesta: 99,07%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8764</t>
+          <t>9476</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2793</t>
+          <t>2767</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10987</t>
+          <t>11145</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6354</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17404</t>
+          <t>16982</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4163</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13157</t>
+          <t>13459</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8392</t>
+          <t>8245</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6935</t>
+          <t>6930</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18282</t>
+          <t>18586</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4212</t>
+          <t>4359</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14151</t>
+          <t>13877</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6936</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17651</t>
+          <t>18069</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13117</t>
+          <t>13550</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>28181</t>
+          <t>27733</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,06%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13667</t>
+          <t>13361</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27143</t>
+          <t>26914</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14303</t>
+          <t>13852</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28549</t>
+          <t>28643</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31081</t>
+          <t>30656</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50546</t>
+          <t>49862</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,09%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>84256</t>
+          <t>83089</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>101829</t>
+          <t>101355</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>91340</t>
+          <t>90198</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>109347</t>
+          <t>109217</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>180871</t>
+          <t>180162</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>206763</t>
+          <t>204670</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>65,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>74,26%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3444</t>
+          <t>3506</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12032</t>
+          <t>11985</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1217</t>
+          <t>1220</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6492</t>
+          <t>6908</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5737</t>
+          <t>5758</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16124</t>
+          <t>15781</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3095</t>
+          <t>3112</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11181</t>
+          <t>11076</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3241</t>
+          <t>2791</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11590</t>
+          <t>11303</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7250</t>
+          <t>7343</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18257</t>
+          <t>19070</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11491</t>
+          <t>11227</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23146</t>
+          <t>23887</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5298</t>
+          <t>4755</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15407</t>
+          <t>14824</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>18616</t>
+          <t>18402</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>33846</t>
+          <t>34760</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17846</t>
+          <t>17466</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32903</t>
+          <t>32598</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16265</t>
+          <t>16316</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30701</t>
+          <t>30796</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37085</t>
+          <t>36194</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>58000</t>
+          <t>56614</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,29%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>127510</t>
+          <t>127023</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>146837</t>
+          <t>147526</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>66,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>153357</t>
+          <t>153384</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>171946</t>
+          <t>172850</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>286406</t>
+          <t>288572</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>314270</t>
+          <t>316878</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>79,97%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2593</t>
+          <t>2705</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11379</t>
+          <t>10456</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3840</t>
+          <t>3808</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3480</t>
+          <t>3630</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11574</t>
+          <t>12339</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3355</t>
+          <t>3057</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>11372</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2126</t>
+          <t>1847</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9072</t>
+          <t>8962</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6109</t>
+          <t>6836</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17053</t>
+          <t>17791</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5632</t>
+          <t>5704</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16154</t>
+          <t>15707</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6143</t>
+          <t>5857</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16912</t>
+          <t>16765</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>14596</t>
+          <t>14842</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>28664</t>
+          <t>28264</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11937</t>
+          <t>12359</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23977</t>
+          <t>24574</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11318</t>
+          <t>11781</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23441</t>
+          <t>23377</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>26599</t>
+          <t>26523</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>44402</t>
+          <t>43464</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>14,98%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>93115</t>
+          <t>92397</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>109472</t>
+          <t>109090</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>77,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>106594</t>
+          <t>106982</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>123552</t>
+          <t>123163</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>71,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>204774</t>
+          <t>205672</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>228852</t>
+          <t>228251</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>78,69%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1668</t>
+          <t>1481</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9722</t>
+          <t>9034</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1603</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9219</t>
+          <t>9898</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5172</t>
+          <t>4484</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15073</t>
+          <t>15361</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5967</t>
+          <t>5755</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17664</t>
+          <t>17818</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>7747</t>
+          <t>7741</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>20205</t>
+          <t>19184</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>15758</t>
+          <t>15683</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>32524</t>
+          <t>32236</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10579</t>
+          <t>10297</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24178</t>
+          <t>24689</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11549</t>
+          <t>10993</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>24297</t>
+          <t>23980</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>25510</t>
+          <t>24841</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>44031</t>
+          <t>44324</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12917</t>
+          <t>13021</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>28137</t>
+          <t>27545</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>16834</t>
+          <t>16505</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>32454</t>
+          <t>31589</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>33873</t>
+          <t>32979</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>56637</t>
+          <t>53837</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,13%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>127829</t>
+          <t>128537</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>149617</t>
+          <t>149069</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>67,2%</t>
+          <t>67,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>78,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>123333</t>
+          <t>123286</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>143763</t>
+          <t>143686</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>257797</t>
+          <t>257600</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>287992</t>
+          <t>288811</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,8%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>14318</t>
+          <t>14648</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>28805</t>
+          <t>30121</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>9693</t>
+          <t>10029</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>22622</t>
+          <t>22858</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>27185</t>
+          <t>27558</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>47928</t>
+          <t>47098</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>23346</t>
+          <t>22843</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>42226</t>
+          <t>40946</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>18931</t>
+          <t>19394</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>36345</t>
+          <t>35539</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>45875</t>
+          <t>45814</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>70293</t>
+          <t>70858</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>40568</t>
+          <t>41796</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>63569</t>
+          <t>64038</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>37715</t>
+          <t>37337</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>59836</t>
+          <t>59945</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>83472</t>
+          <t>82683</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>116383</t>
+          <t>115571</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,61%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>67887</t>
+          <t>67200</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>95719</t>
+          <t>96611</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>70771</t>
+          <t>70625</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>98061</t>
+          <t>99803</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>145193</t>
+          <t>144665</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>183043</t>
+          <t>183470</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,66%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>454107</t>
+          <t>452969</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>490209</t>
+          <t>491484</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>494784</t>
+          <t>495516</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>530838</t>
+          <t>532021</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>958999</t>
+          <t>959177</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1011225</t>
+          <t>1013242</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>75,45%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de tomar yogures en 2016 (tasa de respuesta: 98,69%)</t>
+          <t>Menores según la frecuencia de tomar yogures o petit suises en 2016 (tasa de respuesta: 98,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1870</t>
+          <t>1855</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10355</t>
+          <t>9810</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1464</t>
+          <t>1453</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8368</t>
+          <t>9240</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4923</t>
+          <t>4551</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15591</t>
+          <t>14899</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2667</t>
+          <t>2716</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11227</t>
+          <t>11312</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>965</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8577</t>
+          <t>8515</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,47 +8179,47 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
+          <t>6,19%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>9626</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>5212</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>3,68%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>1,99%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t>6,24%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>9626</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>5426</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>16101</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>3,68%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>2,08%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11379</t>
+          <t>10693</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24479</t>
+          <t>23364</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9513</t>
+          <t>9434</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22469</t>
+          <t>23154</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>23443</t>
+          <t>24276</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>41458</t>
+          <t>42193</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>16,14%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23553</t>
+          <t>23777</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40083</t>
+          <t>40204</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31219</t>
+          <t>31680</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50916</t>
+          <t>49529</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>60177</t>
+          <t>59968</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>84857</t>
+          <t>85412</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,68%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>54633</t>
+          <t>55361</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>74511</t>
+          <t>74501</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>62775</t>
+          <t>64075</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>83627</t>
+          <t>83757</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>124596</t>
+          <t>125441</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>151207</t>
+          <t>152895</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>58,5%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7061</t>
+          <t>7317</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8738,7 +8738,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3727</t>
+          <t>3848</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1673</t>
+          <t>1815</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8013</t>
+          <t>8324</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3733</t>
+          <t>3686</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12548</t>
+          <t>12173</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1572</t>
+          <t>1483</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8952</t>
+          <t>8682</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7180</t>
+          <t>7193</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17595</t>
+          <t>17324</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23340</t>
+          <t>24358</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>39514</t>
+          <t>40431</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>16995</t>
+          <t>16944</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>31947</t>
+          <t>32734</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>43346</t>
+          <t>43972</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>65752</t>
+          <t>66344</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,52%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40856</t>
+          <t>40471</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>58726</t>
+          <t>60131</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49330</t>
+          <t>49424</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69440</t>
+          <t>71610</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>95602</t>
+          <t>95834</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>123436</t>
+          <t>123063</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,65%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>90925</t>
+          <t>89930</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>111653</t>
+          <t>111501</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>110780</t>
+          <t>109549</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>133064</t>
+          <t>132425</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>206748</t>
+          <t>206298</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>238138</t>
+          <t>238149</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,7 +9235,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>1076</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6248</t>
+          <t>6537</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>627</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5303</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,7 +9430,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2265</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9055</t>
+          <t>9460</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>7311</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9533,7 +9533,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4498</t>
+          <t>4405</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9104</t>
+          <t>9115</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9307</t>
+          <t>9502</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20977</t>
+          <t>21081</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7431</t>
+          <t>7863</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18726</t>
+          <t>19506</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>19249</t>
+          <t>20181</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>35175</t>
+          <t>35894</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,88%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14185</t>
+          <t>14074</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27759</t>
+          <t>28318</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24867</t>
+          <t>25878</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>42764</t>
+          <t>43485</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>42991</t>
+          <t>43472</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>65141</t>
+          <t>66158</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,9%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>93780</t>
+          <t>93615</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>111403</t>
+          <t>111081</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>98596</t>
+          <t>98514</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>118700</t>
+          <t>117917</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>62,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>198499</t>
+          <t>196627</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>224180</t>
+          <t>223971</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>74,14%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>728</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7115</t>
+          <t>7531</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2172</t>
+          <t>2175</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9519</t>
+          <t>10305</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3884</t>
+          <t>3969</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13180</t>
+          <t>14261</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4741</t>
+          <t>4237</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14953</t>
+          <t>14358</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4410</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>13794</t>
+          <t>13431</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>10067</t>
+          <t>10222</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>23318</t>
+          <t>23870</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11833</t>
+          <t>12388</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>25512</t>
+          <t>27352</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10930</t>
+          <t>11361</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23801</t>
+          <t>23828</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>26880</t>
+          <t>27131</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>46169</t>
+          <t>44781</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>11,84%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>34787</t>
+          <t>35006</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>55297</t>
+          <t>54115</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>32443</t>
+          <t>32304</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>50568</t>
+          <t>50828</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>71490</t>
+          <t>71237</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>98507</t>
+          <t>98383</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,01%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>103868</t>
+          <t>104355</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>127688</t>
+          <t>126574</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>55,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>106845</t>
+          <t>108057</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>129346</t>
+          <t>128886</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>217679</t>
+          <t>217953</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>248313</t>
+          <t>250764</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>66,29%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9658</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>21862</t>
+          <t>22110</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7073</t>
+          <t>6253</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>18862</t>
+          <t>18173</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>17907</t>
+          <t>18558</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>35827</t>
+          <t>35240</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>17914</t>
+          <t>17823</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>34137</t>
+          <t>33928</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>11241</t>
+          <t>10675</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>25726</t>
+          <t>24747</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>33360</t>
+          <t>32280</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>54808</t>
+          <t>53422</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>68159</t>
+          <t>68539</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>95967</t>
+          <t>95979</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,7 +10985,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>56638</t>
+          <t>56555</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>82323</t>
+          <t>82574</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>132399</t>
+          <t>131689</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>170021</t>
+          <t>168947</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>127409</t>
+          <t>128588</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>162621</t>
+          <t>163246</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>155417</t>
+          <t>155840</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>192881</t>
+          <t>194617</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>297408</t>
+          <t>295819</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>346836</t>
+          <t>348267</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,93%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>363198</t>
+          <t>363911</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>403231</t>
+          <t>400941</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>402414</t>
+          <t>402076</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>444439</t>
+          <t>443818</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>776806</t>
+          <t>776521</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>835638</t>
+          <t>836099</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>57,81%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>62,24%</t>
         </is>
       </c>
     </row>
